--- a/core/VCH_ProjectTemplate.xlsx
+++ b/core/VCH_ProjectTemplate.xlsx
@@ -391,7 +391,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VERIFIABLE COPILOT HARNESS PROJECT TEMPLATE v6.13.0</t>
+          <t>VERIFIABLE COPILOT HARNESS PROJECT TEMPLATE v6.14.0</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Add __ROUTING_ORACLE behavioral regression sheet (out-of-bootstrap) and bump to v6.13.0</t>
+          <t>Add __ROUTING_ORACLE behavioral regression sheet (out-of-bootstrap) and bump to v6.14.0</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Adds one sheet to both HarnessCore and ProjectTemplate; skill count stays 41 (routing oracle is data, not a skill); three ROUTING oracle rows added to __TEST_ORACLE; two glossary terms added (Routing oracle, Behavioral test); Project.Rules gains a ROUTING ORACLE rule; starter, custom instructions and cheatsheet updated to declare the out-of-bootstrap corpus; all components bumped to v6.13.0. ADR-012 supersedes the fixed B32 probe-address assumption in ADR-008; PROBE_CELL resolved by name is authoritative.</t>
+          <t>Adds one sheet to both HarnessCore and ProjectTemplate; skill count stays 41 (routing oracle is data, not a skill); three ROUTING oracle rows added to __TEST_ORACLE; two glossary terms added (Routing oracle, Behavioral test); Project.Rules gains a ROUTING ORACLE rule; starter, custom instructions and cheatsheet updated to declare the out-of-bootstrap corpus; all components bumped to v6.14.0. ADR-012 supersedes the fixed B32 probe-address assumption in ADR-008; PROBE_CELL resolved by name is authoritative.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1592,7 +1592,59 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Independent reopen of both v6.13.0 workbooks; deterministic structural checks: 41 skills, __ROUTING_ORACLE present and out of bootstrap read-set, 0 unresolved Expected_Skill_ID references, 0 duplicate routing Test_ID, version agreement PASS, probe cell intact. Independent read-back confirms PROBE_CELL resolves to __STATE!B31.</t>
+          <t>Independent reopen of both v6.14.0 workbooks; deterministic structural checks: 41 skills, __ROUTING_ORACLE present and out of bootstrap read-set, 0 unresolved Expected_Skill_ID references, 0 duplicate routing Test_ID, version agreement PASS, probe cell intact. Independent read-back confirms PROBE_CELL resolves to __STATE!B31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ADR-013</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Add STATUS and CAPABILITY-DISCOVERY skills plus a mandatory Status Card (43 skills) and bump to v6.14.0</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>External proposal (Grok) reviewed and adapted: a compact Status Card after key events, a cheap read-only STATUS atom, and a conservative context-aware skill discovery. Czech and diacritic trigger atoms were dropped (character policy), the colliding atom 'what can you do now' was dropped (prefix collision with 'what can you do'), and non-ASCII arrows in templates were replaced with -&gt;.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Adopt as proposed; adopt with trigger and ASCII corrections; reject.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Adopted with corrections: the Status Card formalizes state restatement already required by FOCUS-MODE rule 5 and bootstrap discipline; STATUS is cheap and read-only; CAPABILITY-DISCOVERY never suggests skills violating current gates, persistence or runtime capability. All new trigger atoms are unique, prefix-collision-free ASCII English atoms.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Skill count becomes 43 (oracle, _README and lint updated); routing corpus grows to 55 fixtures; custom instructions and starter gain a STATUS CARD contract; cheatsheet and README updated.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Revert to the v6.13.0 artifacts (release assets VCH_v6.13.0.zip).</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Deterministic scan on reopened v6.14.0 workbooks: 43 skills, trigger duplicates 0, prefix collisions 0, non-ASCII cells 0, routing 55/55 refs resolved, probe B31, version agreement v6.14.0.</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2298,6 +2350,38 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Status card</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Mandatory compact status block appended at the very end of replies after key events (bootstrap, guide steps, gates, revision commits, update context, explicit status): Mode, Resume, Gate, Verified (evidence-qualified only), Next.</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>status block</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>prose summary at reply start</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>ADR-013</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -2310,7 +2394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2330,7 +2414,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FROZEN ROUTING ORACLE v6.13.0 (out-of-bootstrap; L2 routing + L3 adversarial)</t>
+          <t>FROZEN ROUTING ORACLE v6.14.0 (out-of-bootstrap; L2 routing + L3 adversarial)</t>
         </is>
       </c>
     </row>
@@ -5137,6 +5221,162 @@
       <c r="J54" s="3" t="inlineStr">
         <is>
           <t>read once; Active_Behavior_Source_Count=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>RT-053</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>literal_trigger</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>ROUTED</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>read-only status card, no writes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>RT-054</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>what can you do</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>literal_trigger</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>CAPABILITY-DISCOVERY</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>ROUTED</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>context-aware discovery, conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>RT-055</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>ALT</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>where are we</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>alt_trigger_atom</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>ROUTED</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>alt of status / where are we / current status</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5173,7 +5413,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SKILL CATALOGUE v6.13.0</t>
+          <t>SKILL CATALOGUE v6.14.0</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5537,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -5367,7 +5607,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -5439,7 +5679,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -5509,7 +5749,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -5579,7 +5819,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -5649,7 +5889,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -5719,7 +5959,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -5789,7 +6029,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -5859,7 +6099,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -5929,7 +6169,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -5999,7 +6239,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -6069,7 +6309,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -6139,7 +6379,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -6209,7 +6449,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -6279,7 +6519,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -6349,7 +6589,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -6419,7 +6659,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -6489,7 +6729,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -6559,7 +6799,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -6629,7 +6869,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -6699,7 +6939,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -6769,7 +7009,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -6839,7 +7079,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -6909,7 +7149,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -6979,7 +7219,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -7049,7 +7289,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -7119,7 +7359,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -7189,7 +7429,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -7259,7 +7499,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -7329,7 +7569,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -7399,7 +7639,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -7469,7 +7709,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -7539,7 +7779,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -7609,7 +7849,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -7679,7 +7919,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -7749,7 +7989,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -7819,7 +8059,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -7889,7 +8129,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -7959,7 +8199,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -8029,7 +8269,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -8099,7 +8339,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -8169,7 +8409,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -8186,6 +8426,150 @@
         <v>96</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>status / where are we / current status</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Read-only current status report (Status Card).</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Read __STATE, gate status and evidence-qualified verified items from the active behavior source; output only the Status Card; never write.</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Status Card fields: Mode, Resume (literal Resume_From or none), Gate (PASS, BLOCKED, NOT_TESTED or n/a), Verified (max 3 INDEPENDENT_READ_BACK or TOOL_TRANSACTION_REPORT items), Next (one concrete action). The card is always the last block; only a short VERSION_MISMATCH or WRITE_BLOCKED warning may precede it.</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Read-only; never writes to the workbook.</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Same behavior in FOCUS MODE; no prose around the card.</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>v6.14.0</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>User asks for a quick reliable current-state overview without further work.</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Do not use to change state or continue delivery.</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>CAPABILITY-DISCOVERY</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Capability Discovery</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>what can you do / available skills</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Context-aware list of skills usable right now.</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Detect workbook mode, open gates, runtime capability and persistence; list only skills allowed now; max 5-6 entries; never the full catalog.</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Output an AVAILABLE NOW block: Mode, High priority (Skill_ID -&gt; shortest trigger and one-line purpose), Also available, Blocked (with reason: gate, mode or capability). Conservative: never suggest skills that would violate current Persistence_Mode, runtime capability or phase gates. In FOCUS MODE shorten further, high priority only.</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Read-only analysis; never writes to the workbook.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Uses runtime capability only; never stored PASS state.</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>v6.14.0</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>User asks which skills make sense right now, not the full catalog.</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Do not use for a full catalog listing or when routing to a specific skill is already clear.</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
@@ -8213,7 +8597,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PROJECT.RULES v6.13.0</t>
+          <t>PROJECT.RULES v6.14.0</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8765,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>All components must agree on v6.13.0.</t>
+          <t>All components must agree on v6.14.0.</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8873,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Use v6.13.0 for all harness and skill versions and NONE for an explicit empty canonical alternative. The strings None and none are forbidden as canonical tokens. Artifact_Status=REJECTED and Output_Verification_Status=OUTPUT_REJECTED are distinct field-scoped states.</t>
+          <t>Use v6.14.0 for all harness and skill versions and NONE for an explicit empty canonical alternative. The strings None and none are forbidden as canonical tokens. Artifact_Status=REJECTED and Output_Verification_Status=OUTPUT_REJECTED are distinct field-scoped states.</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8995,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>__STATE v6.13.0</t>
+          <t>__STATE v6.14.0</t>
         </is>
       </c>
     </row>
@@ -8643,7 +9027,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
     </row>
@@ -8667,7 +9051,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
     </row>
@@ -8799,7 +9183,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>VCH_ProjectTemplate.xlsx v6.12.0</t>
+          <t>VCH_ProjectTemplate.xlsx v6.13.0</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9411,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>VCH_ProjectTemplate.xlsx v6.12.0; ADR-012</t>
+          <t>VCH_ProjectTemplate.xlsx v6.13.0; ADR-013</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9502,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FROZEN TEST ORACLE v6.13.0</t>
+          <t>FROZEN TEST ORACLE v6.14.0</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9853,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -9494,7 +9878,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>00_Skills must have exactly 41 non-empty Skill_ID.</t>
+          <t>00_Skills must have exactly 43 non-empty Skill_ID.</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9900,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -9541,7 +9925,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>All version fields across sheets agree on v6.13.0.</t>
+          <t>All version fields across sheets agree on v6.14.0.</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9947,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>v6.13.0</t>
+          <t>v6.14.0</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -9588,7 +9972,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>All 41 skill rows use canonical v6.13.0.</t>
+          <t>All 43 skill rows use canonical v6.14.0.</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10749,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CANONICAL LISTS v6.13.0</t>
+          <t>CANONICAL LISTS v6.14.0</t>
         </is>
       </c>
     </row>

--- a/core/VCH_ProjectTemplate.xlsx
+++ b/core/VCH_ProjectTemplate.xlsx
@@ -391,7 +391,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VERIFIABLE COPILOT HARNESS PROJECT TEMPLATE v6.14.0</t>
+          <t>VERIFIABLE COPILOT HARNESS PROJECT TEMPLATE v6.15.0</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Add __ROUTING_ORACLE behavioral regression sheet (out-of-bootstrap) and bump to v6.14.0</t>
+          <t>Add __ROUTING_ORACLE behavioral regression sheet (out-of-bootstrap) and bump to v6.15.0</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Adds one sheet to both HarnessCore and ProjectTemplate; skill count stays 41 (routing oracle is data, not a skill); three ROUTING oracle rows added to __TEST_ORACLE; two glossary terms added (Routing oracle, Behavioral test); Project.Rules gains a ROUTING ORACLE rule; starter, custom instructions and cheatsheet updated to declare the out-of-bootstrap corpus; all components bumped to v6.14.0. ADR-012 supersedes the fixed B32 probe-address assumption in ADR-008; PROBE_CELL resolved by name is authoritative.</t>
+          <t>Adds one sheet to both HarnessCore and ProjectTemplate; skill count stays 41 (routing oracle is data, not a skill); three ROUTING oracle rows added to __TEST_ORACLE; two glossary terms added (Routing oracle, Behavioral test); Project.Rules gains a ROUTING ORACLE rule; starter, custom instructions and cheatsheet updated to declare the out-of-bootstrap corpus; all components bumped to v6.15.0. ADR-012 supersedes the fixed B32 probe-address assumption in ADR-008; PROBE_CELL resolved by name is authoritative.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Independent reopen of both v6.14.0 workbooks; deterministic structural checks: 41 skills, __ROUTING_ORACLE present and out of bootstrap read-set, 0 unresolved Expected_Skill_ID references, 0 duplicate routing Test_ID, version agreement PASS, probe cell intact. Independent read-back confirms PROBE_CELL resolves to __STATE!B31.</t>
+          <t>Independent reopen of both v6.15.0 workbooks; deterministic structural checks: 41 skills, __ROUTING_ORACLE present and out of bootstrap read-set, 0 unresolved Expected_Skill_ID references, 0 duplicate routing Test_ID, version agreement PASS, probe cell intact. Independent read-back confirms PROBE_CELL resolves to __STATE!B31.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Add STATUS and CAPABILITY-DISCOVERY skills plus a mandatory Status Card (43 skills) and bump to v6.14.0</t>
+          <t>Add STATUS and CAPABILITY-DISCOVERY skills plus a mandatory Status Card (43 skills) and bump to v6.15.0</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1644,7 +1644,59 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Deterministic scan on reopened v6.14.0 workbooks: 43 skills, trigger duplicates 0, prefix collisions 0, non-ASCII cells 0, routing 55/55 refs resolved, probe B31, version agreement v6.14.0.</t>
+          <t>Deterministic scan on reopened v6.15.0 workbooks: 43 skills, trigger duplicates 0, prefix collisions 0, non-ASCII cells 0, routing 55/55 refs resolved, probe B31, version agreement v6.15.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ADR-014</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Add Allowed_Modes column to 00_Skills for deterministic mode-based skill filtering and bump to v6.15.0</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>CAPABILITY-DISCOVERY (ADR-013) judged mode eligibility from Use_When prose, which is soft. A machine-readable allowlist makes mode filtering deterministic and lint-enforceable.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Prose-only filtering; Allowed_Modes column with ALL or an explicit mode subset.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>A catalog column is declarative, validated by the deterministic lint, and keeps CAPABILITY-DISCOVERY conservative by construction: persistence skills are PROJECT-only, forking is TEMPLATE, PROJECT-CREATION and MIGRATION only, orchestration stays with project modes.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>00_Skills gains column Allowed_Modes (ALL or comma-space separated subset of HARNESS, TEMPLATE, PROJECT-CREATION, PROJECT, MIGRATION); Project.Rules gains ALLOWED MODES; oracle gains Allowed_Modes_Valid DETERMINISTIC_SCAN; harness_lint validates values; CAPABILITY-DISCOVERY behavior now references the column.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Revert to the v6.14.0 artifacts (release assets VCH_v6.14.0.zip).</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Deterministic scan on reopened v6.15.0 workbooks: 43 skills, Allowed_Modes 43/43 valid, trigger duplicates 0, prefix collisions 0, non-ASCII 0, routing 55/55 refs resolved, probe B31, version agreement v6.15.0.</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2377,6 +2429,38 @@
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Allowed modes</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>00_Skills.Allowed_Modes value declaring in which workbook modes a skill may run: ALL or a comma-space separated subset of HARNESS, TEMPLATE, PROJECT-CREATION, PROJECT, MIGRATION. Routing and CAPABILITY-DISCOVERY must not propose a skill outside its Allowed_Modes.</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>mode allowlist</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>soft prose-based filtering</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>ADR-014</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
@@ -2414,7 +2498,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FROZEN ROUTING ORACLE v6.14.0 (out-of-bootstrap; L2 routing + L3 adversarial)</t>
+          <t>FROZEN ROUTING ORACLE v6.15.0 (out-of-bootstrap; L2 routing + L3 adversarial)</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5413,7 +5497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SKILL CATALOGUE v6.14.0</t>
+          <t>SKILL CATALOGUE v6.15.0</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5621,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -5558,6 +5642,11 @@
           <t>BOOTSTRAP-CHECK, CAPABILITY-ROUTER</t>
         </is>
       </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Allowed_Modes</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="23.85" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -5607,7 +5696,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -5628,6 +5717,11 @@
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>BOOTSTRAP-CHECK, CAPABILITY-ROUTER</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5773,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -5700,6 +5794,11 @@
           <t>GRILL-ME</t>
         </is>
       </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="35.1" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -5749,7 +5848,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -5770,6 +5869,11 @@
           <t>SHAPING</t>
         </is>
       </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23.85" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -5819,7 +5923,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -5840,6 +5944,11 @@
           <t>SHAPING</t>
         </is>
       </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="23.85" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -5889,7 +5998,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -5910,6 +6019,11 @@
           <t>SHAPING</t>
         </is>
       </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="23.85" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -5959,7 +6073,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -5980,6 +6094,11 @@
           <t>UPDATE-CONTEXT</t>
         </is>
       </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="23.85" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -6029,7 +6148,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -6050,6 +6169,11 @@
           <t>WRITING-PITCH</t>
         </is>
       </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23.85" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -6099,7 +6223,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -6120,6 +6244,11 @@
           <t>PROOF</t>
         </is>
       </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -6169,7 +6298,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -6190,6 +6319,11 @@
           <t>WRITING-PLANS</t>
         </is>
       </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="23.85" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -6239,7 +6373,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -6260,6 +6394,11 @@
           <t>PLAN-DEEPENING</t>
         </is>
       </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23.85" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -6309,7 +6448,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -6330,6 +6469,11 @@
           <t>VERIFICATION-CHECKLIST</t>
         </is>
       </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="23.85" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -6379,7 +6523,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -6400,6 +6544,11 @@
           <t>VERIFICATION-CHECKLIST</t>
         </is>
       </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.85" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -6449,7 +6598,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -6470,6 +6619,11 @@
           <t>UPDATE-CONTEXT</t>
         </is>
       </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="23.85" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -6519,7 +6673,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -6540,6 +6694,11 @@
           <t>SCRUB</t>
         </is>
       </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="23.85" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -6589,7 +6748,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -6610,6 +6769,11 @@
           <t>COMPOUND</t>
         </is>
       </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.85" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -6659,7 +6823,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -6680,6 +6844,11 @@
           <t>HARDEN-SCRIPT</t>
         </is>
       </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23.85" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -6729,7 +6898,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -6750,6 +6919,11 @@
           <t>SHAPING</t>
         </is>
       </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.85" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -6799,7 +6973,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -6820,6 +6994,11 @@
           <t>SHAPING</t>
         </is>
       </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="23.85" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -6869,7 +7048,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -6890,6 +7069,11 @@
           <t>VERIFICATION-CHECKLIST</t>
         </is>
       </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="23.85" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -6939,7 +7123,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -6960,6 +7144,11 @@
           <t>COMPOUND</t>
         </is>
       </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="23.85" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -7009,7 +7198,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -7030,6 +7219,11 @@
           <t>BUILD-TOOL</t>
         </is>
       </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23.85" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -7079,7 +7273,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -7100,6 +7294,11 @@
           <t>PROOF</t>
         </is>
       </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23.85" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -7149,7 +7348,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -7170,6 +7369,11 @@
           <t>HARDEN-SCRIPT</t>
         </is>
       </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="23.85" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -7219,7 +7423,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -7240,6 +7444,11 @@
           <t>SCRUB</t>
         </is>
       </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="23.85" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -7289,7 +7498,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -7310,6 +7519,11 @@
           <t>WRITING-PLANS</t>
         </is>
       </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="23.85" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -7359,7 +7573,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -7380,6 +7594,11 @@
           <t>UPDATE-CONTEXT</t>
         </is>
       </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="23.85" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -7429,7 +7648,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -7450,6 +7669,11 @@
           <t>PROOF</t>
         </is>
       </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23.85" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -7499,7 +7723,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -7520,6 +7744,11 @@
           <t>CAPABILITY-ROUTER</t>
         </is>
       </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="35.1" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -7569,7 +7798,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -7590,6 +7819,11 @@
           <t>WRITING-PLANS</t>
         </is>
       </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>TEMPLATE, PROJECT-CREATION, MIGRATION</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="23.85" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -7639,7 +7873,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -7660,6 +7894,11 @@
           <t>UPDATE-CONTEXT</t>
         </is>
       </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="35.1" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -7709,7 +7948,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -7730,6 +7969,11 @@
           <t>PROJECT-FORK, ACTIVATE-PRECOPIED-REVISION, INPLACE-CHECKPOINT</t>
         </is>
       </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="35.1" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -7779,7 +8023,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -7800,6 +8044,11 @@
           <t>UPDATE-CONTEXT</t>
         </is>
       </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="35.1" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
@@ -7849,7 +8098,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -7870,6 +8119,11 @@
           <t>UPDATE-CONTEXT</t>
         </is>
       </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="35.1" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -7919,7 +8173,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -7940,6 +8194,11 @@
           <t>TRIAGE</t>
         </is>
       </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="23.85" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -7989,7 +8248,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -8010,6 +8269,11 @@
           <t>VERIFICATION-CHECKLIST</t>
         </is>
       </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="35.1" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -8059,7 +8323,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -8080,6 +8344,11 @@
           <t>COMPARE</t>
         </is>
       </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="23.85" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -8129,7 +8398,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -8150,6 +8419,11 @@
           <t>COMPOUND</t>
         </is>
       </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="23.85" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -8199,7 +8473,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -8220,6 +8494,11 @@
           <t>HARDEN-SCRIPT</t>
         </is>
       </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="90.95" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -8269,7 +8548,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -8290,6 +8569,11 @@
           <t>WRITING-PLANS</t>
         </is>
       </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="68.65000000000001" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -8339,7 +8623,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -8360,6 +8644,11 @@
           <t>PROJECT-FORK, CAPABILITY-ROUTER, GRILL-ME, IDEATE, SHAPING, WRITING-PLANS, PLAN-DEEPENING, SYSTEMATIC-DEBUGGING, BUILD-TOOL, HARDEN-SCRIPT, VERIFICATION-CHECKLIST, SCRUB, COMPOUND, DECISION-DRIFT-CHECK, UPDATE-CONTEXT</t>
         </is>
       </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT, PROJECT-CREATION, MIGRATION</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -8409,7 +8698,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -8430,6 +8719,11 @@
           <t>NONE</t>
         </is>
       </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -8479,7 +8773,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -8500,6 +8794,11 @@
       <c r="N45" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8840,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Read-only analysis; never writes to the workbook.</t>
+          <t>Output an AVAILABLE NOW block: Mode, High priority (Skill_ID -&gt; shortest trigger and one-line purpose), Also available, Blocked (with reason: gate, mode or capability). Filter first by the Allowed_Modes column against the current workbook mode, then by gates and runtime capability. Conservative: never suggest skills that would violate current Persistence_Mode, runtime capability or phase gates. In FOCUS MODE shorten further, high priority only.</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -8551,7 +8850,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -8572,6 +8871,11 @@
       <c r="N46" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8597,7 +8901,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PROJECT.RULES v6.14.0</t>
+          <t>PROJECT.RULES v6.15.0</t>
         </is>
       </c>
     </row>
@@ -8765,7 +9069,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>All components must agree on v6.14.0.</t>
+          <t>All components must agree on v6.15.0.</t>
         </is>
       </c>
     </row>
@@ -8873,7 +9177,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Use v6.14.0 for all harness and skill versions and NONE for an explicit empty canonical alternative. The strings None and none are forbidden as canonical tokens. Artifact_Status=REJECTED and Output_Verification_Status=OUTPUT_REJECTED are distinct field-scoped states.</t>
+          <t>Use v6.15.0 for all harness and skill versions and NONE for an explicit empty canonical alternative. The strings None and none are forbidden as canonical tokens. Artifact_Status=REJECTED and Output_Verification_Status=OUTPUT_REJECTED are distinct field-scoped states.</t>
         </is>
       </c>
     </row>
@@ -8970,6 +9274,18 @@
       <c r="B32" s="3" t="inlineStr">
         <is>
           <t>__ROUTING_ORACLE is a frozen behavioral regression corpus (L2 routing, L3 adversarial). It is NOT part of the bootstrap read-set and must not be read on load vch. Run it only on explicit request or before promoting a catalogue change. Every Expected_Skill_ID must be NONE or an existing Skill_ID. Model routing runs are behavioral tests; harness_lint validates only structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>ALLOWED MODES</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>00_Skills.Allowed_Modes declares in which workbook modes a skill may run: ALL or a comma-space separated subset of HARNESS, TEMPLATE, PROJECT-CREATION, PROJECT, MIGRATION. Routing and CAPABILITY-DISCOVERY must not propose a skill outside its Allowed_Modes.</t>
         </is>
       </c>
     </row>
@@ -8995,7 +9311,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>__STATE v6.14.0</t>
+          <t>__STATE v6.15.0</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9343,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9367,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9499,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>VCH_ProjectTemplate.xlsx v6.13.0</t>
+          <t>VCH_ProjectTemplate.xlsx v6.14.0</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9727,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>VCH_ProjectTemplate.xlsx v6.13.0; ADR-013</t>
+          <t>VCH_ProjectTemplate.xlsx v6.14.0; ADR-014</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9502,7 +9818,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FROZEN TEST ORACLE v6.14.0</t>
+          <t>FROZEN TEST ORACLE v6.15.0</t>
         </is>
       </c>
     </row>
@@ -9900,7 +10216,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -9925,7 +10241,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>All version fields across sheets agree on v6.14.0.</t>
+          <t>All version fields across sheets agree on v6.15.0.</t>
         </is>
       </c>
     </row>
@@ -9947,7 +10263,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>v6.14.0</t>
+          <t>v6.15.0</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -9972,7 +10288,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>All 43 skill rows use canonical v6.14.0.</t>
+          <t>All 43 skill rows use canonical v6.15.0.</t>
         </is>
       </c>
     </row>
@@ -10725,6 +11041,53 @@
       <c r="I27" s="3" t="inlineStr">
         <is>
           <t>All __ROUTING_ORACLE Test_ID values are unique. Structural check only; behavioral routing requires an isolated routing run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>NORMALIZATION</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Allowed_Modes_Valid</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>DETERMINISTIC_SCAN</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Every 00_Skills.Allowed_Modes value is ALL or a comma-space separated subset of HARNESS, TEMPLATE, PROJECT-CREATION, PROJECT, MIGRATION.</t>
         </is>
       </c>
     </row>
@@ -10749,7 +11112,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CANONICAL LISTS v6.14.0</t>
+          <t>CANONICAL LISTS v6.15.0</t>
         </is>
       </c>
     </row>
